--- a/public/post/drafts/race-prediction/men_simple-model-tests-actual_rmse.xlsx
+++ b/public/post/drafts/race-prediction/men_simple-model-tests-actual_rmse.xlsx
@@ -610,25 +610,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.182426886141633</v>
+        <v>0.177597103383836</v>
       </c>
       <c r="C9" t="n">
-        <v>0.136517622751171</v>
+        <v>0.137445306104841</v>
       </c>
       <c r="D9" t="n">
-        <v>0.21236949108517</v>
+        <v>0.211035216538377</v>
       </c>
       <c r="E9" t="n">
-        <v>0.178372924940222</v>
+        <v>0.181176625633318</v>
       </c>
       <c r="F9" t="n">
-        <v>0.189352823257298</v>
+        <v>0.19108656626583</v>
       </c>
       <c r="G9" t="n">
-        <v>0.162939994426569</v>
+        <v>0.164932592073655</v>
       </c>
       <c r="H9" t="n">
-        <v>0.176996623767011</v>
+        <v>0.177212234999976</v>
       </c>
     </row>
     <row r="10">
